--- a/asset-forge/products/industries/hospitality/boutique-hotel-4star/05_Operations.xlsx
+++ b/asset-forge/products/industries/hospitality/boutique-hotel-4star/05_Operations.xlsx
@@ -2719,21 +2719,21 @@
     <row r="42" ht="30" customHeight="1">
       <c r="B42" s="52" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ADR/occupancy/RevPAR benchmarks: Fáilte Ireland &amp; STR Ireland hotel performance reports (4-star/boutique ranges).</t>
+          <t xml:space="preserve">  ADR/occupancy/RevPAR: Fáilte Ireland Hotel Survey 2024 — 4★ ADR €143.50–€144.49, occupancy 60.2% (Dec) → 74.1% (Nov), RevPAR €86.42–€107.07.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="B43" s="52" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Grant/funding figures: Local Enterprise Office (localenterprise.ie), Microfinance Ireland, SBCI, Fáilte Ireland investment schemes.</t>
+          <t xml:space="preserve">  Cost ratios: hospitality labour 25–35% of revenue (US long-run 31.2%); USALI F&amp;B cost-of-sales; GOP margin ~36–38% (HotelData 2025). See `startup_benchmarks` table.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="B44" s="52" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Cost ratios (payroll ~30%, F&amp;B cost ~30%): USALI hotel P&amp;L conventions.</t>
+          <t xml:space="preserve">  Grant/funding figures: Local Enterprise Office (localenterprise.ie), Microfinance Ireland, SBCI, Fáilte Ireland investment schemes.</t>
         </is>
       </c>
     </row>
